--- a/产业趋势研究&选股/美国通胀压力温度计/美国通胀压力温度计_试算_20261011.xlsx
+++ b/产业趋势研究&选股/美国通胀压力温度计/美国通胀压力温度计_试算_20261011.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="看板" sheetId="1" r:id="Rfce448caef344518"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子数据" sheetId="2" r:id="R6d9132520bc244cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子4明细" sheetId="3" r:id="R3aa9c342b7524a92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径与来源" sheetId="4" r:id="Raac1fcdd82d34d50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="看板" sheetId="1" r:id="Rc693a6d98ec24d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子数据" sheetId="2" r:id="R6f3884b6bcb04f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="因子4明细" sheetId="3" r:id="R6b07164f70744956"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径与来源" sheetId="4" r:id="Rb4119545a61c44fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -390,7 +390,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="26" t="str">
-        <x:v>基准：2022 年 1–6 月月均值=100；四因子等权。最新可得值存在一个月错位。</x:v>
+        <x:v>基准：2022 年 1–6 月月均值=100；四因子等权。</x:v>
       </x:c>
       <x:c r="B2" s="26"/>
       <x:c r="C2" s="26"/>
@@ -426,7 +426,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>最新可得观察：Atlanta Fed WGT 为 2026-09，其余因子为 2026-08</x:v>
+        <x:v>最新可得观察：四因子均为 2026-09</x:v>
       </x:c>
       <x:c r="B4" s="14"/>
       <x:c r="C4" s="14"/>
@@ -523,11 +523,11 @@
       </x:c>
       <x:c r="C7" s="29" t="n">
         <x:f>'因子数据'!L6</x:f>
-        <x:v>2.741335256</x:v>
+        <x:v>2.81553373</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
         <x:f>'因子数据'!M6</x:f>
-        <x:v>2026-08</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E7" s="29" t="n">
         <x:f>'因子数据'!I6</x:f>
@@ -535,11 +535,11 @@
       </x:c>
       <x:c r="F7" s="29" t="n">
         <x:f>C7/E7*100</x:f>
-        <x:v>56.740547731742616</x:v>
+        <x:v>58.276318318869755</x:v>
       </x:c>
       <x:c r="G7" s="29" t="n">
         <x:f>F7/4</x:f>
-        <x:v>14.185136932935654</x:v>
+        <x:v>14.569079579717439</x:v>
       </x:c>
       <x:c r="H7" s="1"/>
       <x:c r="I7" s="1"/>
@@ -561,11 +561,11 @@
       </x:c>
       <x:c r="C8" s="29" t="n">
         <x:f>'因子数据'!L7</x:f>
-        <x:v>4.942421343</x:v>
+        <x:v>6.123248688</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
         <x:f>'因子数据'!M7</x:f>
-        <x:v>2026-08</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E8" s="29" t="n">
         <x:f>'因子数据'!I7</x:f>
@@ -573,11 +573,11 @@
       </x:c>
       <x:c r="F8" s="29" t="n">
         <x:f>C8/E8*100</x:f>
-        <x:v>27.756700060417884</x:v>
+        <x:v>34.38824119454749</x:v>
       </x:c>
       <x:c r="G8" s="29" t="n">
         <x:f>F8/4</x:f>
-        <x:v>6.939175015104471</x:v>
+        <x:v>8.597060298636872</x:v>
       </x:c>
       <x:c r="H8" s="1"/>
       <x:c r="I8" s="1"/>
@@ -599,11 +599,11 @@
       </x:c>
       <x:c r="C9" s="29" t="n">
         <x:f>'因子数据'!L8</x:f>
-        <x:v>50</x:v>
+        <x:v>47.59036144578313</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
         <x:f>'因子数据'!M8</x:f>
-        <x:v>2026-08</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E9" s="29" t="n">
         <x:f>'因子数据'!I8</x:f>
@@ -611,11 +611,11 @@
       </x:c>
       <x:c r="F9" s="29" t="n">
         <x:f>C9/E9*100</x:f>
-        <x:v>65.9403915225613</x:v>
+        <x:v>62.76254132870292</x:v>
       </x:c>
       <x:c r="G9" s="29" t="n">
         <x:f>F9/4</x:f>
-        <x:v>16.485097880640325</x:v>
+        <x:v>15.69063533217573</x:v>
       </x:c>
       <x:c r="H9" s="1"/>
       <x:c r="I9" s="1"/>
@@ -636,11 +636,11 @@
       <x:c r="E10" s="30"/>
       <x:c r="F10" s="30" t="n">
         <x:f>SUM(G6:G9)</x:f>
-        <x:v>53.769630823155595</x:v>
+        <x:v>55.016996205005185</x:v>
       </x:c>
       <x:c r="G10" s="30" t="n">
         <x:f>SUM(G6:G9)</x:f>
-        <x:v>53.769630823155595</x:v>
+        <x:v>55.016996205005185</x:v>
       </x:c>
       <x:c r="H10" s="1"/>
       <x:c r="I10" s="1"/>
@@ -670,7 +670,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>同月对齐观察：四因子均为 2026-08</x:v>
+        <x:v>前月对齐观察：四因子均为 2026-08</x:v>
       </x:c>
       <x:c r="B12" s="14"/>
       <x:c r="C12" s="14"/>
@@ -929,7 +929,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="26" t="str">
-        <x:v>因子4（2026-08）：82 / 164 = 50.0%；170 个映射项目覆盖 BLS 211 项标准的 80.6%，本期数值覆盖为 164 / 211 = 77.7%。</x:v>
+        <x:v>因子4（2026-09）：79 / 166 = 47.6%；170 个映射项目覆盖 BLS 211 项标准的 80.6%，本期数值覆盖为 166 / 211 = 78.7%。</x:v>
       </x:c>
       <x:c r="B21" s="26"/>
       <x:c r="C21" s="26"/>
@@ -967,7 +967,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="26" t="str">
-        <x:v>数据精度：BLS分项同比按页面显示的一位小数近似；最新总分和 2026-08 对齐总分分别显示在上表。</x:v>
+        <x:v>数据精度：BLS分项同比按页面显示的一位小数近似；显示为破折号或空白的项目均不计入分子和分母。</x:v>
       </x:c>
       <x:c r="B23" s="26"/>
       <x:c r="C23" s="26"/>
@@ -4546,13 +4546,15 @@
       <x:c r="J6" s="22" t="n">
         <x:v>2.741335256</x:v>
       </x:c>
-      <x:c r="K6" s="22"/>
+      <x:c r="K6" s="22" t="n">
+        <x:v>2.81553373</x:v>
+      </x:c>
       <x:c r="L6" s="22" t="n">
         <x:f>IF(K6="",J6,K6)</x:f>
-        <x:v>2.741335256</x:v>
+        <x:v>2.81553373</x:v>
       </x:c>
       <x:c r="M6" s="18" t="str">
-        <x:v>2026-08</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="N6" s="18" t="str">
         <x:v>https://fred.stlouisfed.org/data/STICKCPIM159SFRBATL</x:v>
@@ -4591,13 +4593,15 @@
       <x:c r="J7" s="22" t="n">
         <x:v>4.942421343</x:v>
       </x:c>
-      <x:c r="K7" s="22"/>
+      <x:c r="K7" s="22" t="n">
+        <x:v>6.123248688</x:v>
+      </x:c>
       <x:c r="L7" s="22" t="n">
         <x:f>IF(K7="",J7,K7)</x:f>
-        <x:v>4.942421343</x:v>
+        <x:v>6.123248688</x:v>
       </x:c>
       <x:c r="M7" s="18" t="str">
-        <x:v>2026-08</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="N7" s="18" t="str">
         <x:v>https://fred.stlouisfed.org/data/FLEXCPIM159SFRBATL</x:v>
@@ -4643,13 +4647,16 @@
         <x:f>'因子4明细'!J179*100</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K8" s="24"/>
+      <x:c r="K8" s="24" t="n">
+        <x:f>'因子4明细'!L179*100</x:f>
+        <x:v>47.59036144578313</x:v>
+      </x:c>
       <x:c r="L8" s="24" t="n">
         <x:f>IF(K8="",J8,K8)</x:f>
-        <x:v>50</x:v>
+        <x:v>47.59036144578313</x:v>
       </x:c>
       <x:c r="M8" s="23" t="str">
-        <x:v>2026-08</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="N8" s="23" t="str">
         <x:v>https://www.bls.gov/news.release/cpi.t02.htm</x:v>
@@ -8283,6 +8290,8 @@
     <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -8374,8 +8383,12 @@
       <x:c r="K4" s="11" t="str">
         <x:v>2026-08是否&gt;3%</x:v>
       </x:c>
-      <x:c r="L4" s="1"/>
-      <x:c r="M4" s="1"/>
+      <x:c r="L4" s="11" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="M4" s="11" t="str">
+        <x:v>2026-09是否&gt;3%</x:v>
+      </x:c>
       <x:c r="N4" s="1"/>
       <x:c r="O4" s="1"/>
     </x:row>
@@ -8414,8 +8427,13 @@
         <x:f>IF(ISNUMBER(J5),IF(J5&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L5" s="1"/>
-      <x:c r="M5" s="1"/>
+      <x:c r="L5" s="19" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="M5" s="18" t="str">
+        <x:f>IF(ISNUMBER(L5),IF(L5&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N5" s="1"/>
       <x:c r="O5" s="1"/>
     </x:row>
@@ -8454,8 +8472,13 @@
         <x:f>IF(ISNUMBER(J6),IF(J6&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L6" s="1"/>
-      <x:c r="M6" s="1"/>
+      <x:c r="L6" s="19" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="M6" s="18" t="str">
+        <x:f>IF(ISNUMBER(L6),IF(L6&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N6" s="1"/>
       <x:c r="O6" s="1"/>
     </x:row>
@@ -8494,8 +8517,13 @@
         <x:f>IF(ISNUMBER(J7),IF(J7&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L7" s="1"/>
-      <x:c r="M7" s="1"/>
+      <x:c r="L7" s="19" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="M7" s="18" t="str">
+        <x:f>IF(ISNUMBER(L7),IF(L7&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N7" s="1"/>
       <x:c r="O7" s="1"/>
     </x:row>
@@ -8534,8 +8562,13 @@
         <x:f>IF(ISNUMBER(J8),IF(J8&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L8" s="1"/>
-      <x:c r="M8" s="1"/>
+      <x:c r="L8" s="19" t="n">
+        <x:v>-1.3</x:v>
+      </x:c>
+      <x:c r="M8" s="18" t="str">
+        <x:f>IF(ISNUMBER(L8),IF(L8&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N8" s="1"/>
       <x:c r="O8" s="1"/>
     </x:row>
@@ -8574,8 +8607,13 @@
         <x:f>IF(ISNUMBER(J9),IF(J9&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L9" s="1"/>
-      <x:c r="M9" s="1"/>
+      <x:c r="L9" s="19" t="n">
+        <x:v>-0.4</x:v>
+      </x:c>
+      <x:c r="M9" s="18" t="str">
+        <x:f>IF(ISNUMBER(L9),IF(L9&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N9" s="1"/>
       <x:c r="O9" s="1"/>
     </x:row>
@@ -8614,8 +8652,13 @@
         <x:f>IF(ISNUMBER(J10),IF(J10&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L10" s="1"/>
-      <x:c r="M10" s="1"/>
+      <x:c r="L10" s="19" t="n">
+        <x:v>-4.2</x:v>
+      </x:c>
+      <x:c r="M10" s="18" t="str">
+        <x:f>IF(ISNUMBER(L10),IF(L10&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N10" s="1"/>
       <x:c r="O10" s="1"/>
     </x:row>
@@ -8654,8 +8697,13 @@
         <x:f>IF(ISNUMBER(J11),IF(J11&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L11" s="1"/>
-      <x:c r="M11" s="1"/>
+      <x:c r="L11" s="19" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="str">
+        <x:f>IF(ISNUMBER(L11),IF(L11&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N11" s="1"/>
       <x:c r="O11" s="1"/>
     </x:row>
@@ -8694,8 +8742,13 @@
         <x:f>IF(ISNUMBER(J12),IF(J12&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L12" s="1"/>
-      <x:c r="M12" s="1"/>
+      <x:c r="L12" s="19" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="M12" s="18" t="str">
+        <x:f>IF(ISNUMBER(L12),IF(L12&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N12" s="1"/>
       <x:c r="O12" s="1"/>
     </x:row>
@@ -8734,8 +8787,13 @@
         <x:f>IF(ISNUMBER(J13),IF(J13&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L13" s="1"/>
-      <x:c r="M13" s="1"/>
+      <x:c r="L13" s="19" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="M13" s="18" t="str">
+        <x:f>IF(ISNUMBER(L13),IF(L13&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N13" s="1"/>
       <x:c r="O13" s="1"/>
     </x:row>
@@ -8774,8 +8832,13 @@
         <x:f>IF(ISNUMBER(J14),IF(J14&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L14" s="1"/>
-      <x:c r="M14" s="1"/>
+      <x:c r="L14" s="19" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="M14" s="18" t="str">
+        <x:f>IF(ISNUMBER(L14),IF(L14&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N14" s="1"/>
       <x:c r="O14" s="1"/>
     </x:row>
@@ -8814,8 +8877,13 @@
         <x:f>IF(ISNUMBER(J15),IF(J15&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L15" s="1"/>
-      <x:c r="M15" s="1"/>
+      <x:c r="L15" s="19" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="M15" s="18" t="str">
+        <x:f>IF(ISNUMBER(L15),IF(L15&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N15" s="1"/>
       <x:c r="O15" s="1"/>
     </x:row>
@@ -8854,8 +8922,13 @@
         <x:f>IF(ISNUMBER(J16),IF(J16&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L16" s="1"/>
-      <x:c r="M16" s="1"/>
+      <x:c r="L16" s="19" t="n">
+        <x:v>6.3</x:v>
+      </x:c>
+      <x:c r="M16" s="18" t="str">
+        <x:f>IF(ISNUMBER(L16),IF(L16&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N16" s="1"/>
       <x:c r="O16" s="1"/>
     </x:row>
@@ -8894,8 +8967,13 @@
         <x:f>IF(ISNUMBER(J17),IF(J17&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L17" s="1"/>
-      <x:c r="M17" s="1"/>
+      <x:c r="L17" s="19" t="n">
+        <x:v>11.8</x:v>
+      </x:c>
+      <x:c r="M17" s="18" t="str">
+        <x:f>IF(ISNUMBER(L17),IF(L17&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N17" s="1"/>
       <x:c r="O17" s="1"/>
     </x:row>
@@ -8934,8 +9012,13 @@
         <x:f>IF(ISNUMBER(J18),IF(J18&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L18" s="1"/>
-      <x:c r="M18" s="1"/>
+      <x:c r="L18" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M18" s="18" t="str">
+        <x:f>IF(ISNUMBER(L18),IF(L18&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N18" s="1"/>
       <x:c r="O18" s="1"/>
     </x:row>
@@ -8974,8 +9057,13 @@
         <x:f>IF(ISNUMBER(J19),IF(J19&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L19" s="1"/>
-      <x:c r="M19" s="1"/>
+      <x:c r="L19" s="19" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="M19" s="18" t="str">
+        <x:f>IF(ISNUMBER(L19),IF(L19&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N19" s="1"/>
       <x:c r="O19" s="1"/>
     </x:row>
@@ -9014,8 +9102,13 @@
         <x:f>IF(ISNUMBER(J20),IF(J20&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L20" s="1"/>
-      <x:c r="M20" s="1"/>
+      <x:c r="L20" s="19" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="M20" s="18" t="str">
+        <x:f>IF(ISNUMBER(L20),IF(L20&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N20" s="1"/>
       <x:c r="O20" s="1"/>
     </x:row>
@@ -9054,8 +9147,13 @@
         <x:f>IF(ISNUMBER(J21),IF(J21&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L21" s="1"/>
-      <x:c r="M21" s="1"/>
+      <x:c r="L21" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="M21" s="18" t="str">
+        <x:f>IF(ISNUMBER(L21),IF(L21&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N21" s="1"/>
       <x:c r="O21" s="1"/>
     </x:row>
@@ -9094,8 +9192,13 @@
         <x:f>IF(ISNUMBER(J22),IF(J22&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L22" s="1"/>
-      <x:c r="M22" s="1"/>
+      <x:c r="L22" s="19" t="n">
+        <x:v>12.7</x:v>
+      </x:c>
+      <x:c r="M22" s="18" t="str">
+        <x:f>IF(ISNUMBER(L22),IF(L22&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N22" s="1"/>
       <x:c r="O22" s="1"/>
     </x:row>
@@ -9134,8 +9237,13 @@
         <x:f>IF(ISNUMBER(J23),IF(J23&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L23" s="1"/>
-      <x:c r="M23" s="1"/>
+      <x:c r="L23" s="19" t="n">
+        <x:v>16.2</x:v>
+      </x:c>
+      <x:c r="M23" s="18" t="str">
+        <x:f>IF(ISNUMBER(L23),IF(L23&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N23" s="1"/>
       <x:c r="O23" s="1"/>
     </x:row>
@@ -9174,8 +9282,13 @@
         <x:f>IF(ISNUMBER(J24),IF(J24&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L24" s="1"/>
-      <x:c r="M24" s="1"/>
+      <x:c r="L24" s="19" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="M24" s="18" t="str">
+        <x:f>IF(ISNUMBER(L24),IF(L24&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N24" s="1"/>
       <x:c r="O24" s="1"/>
     </x:row>
@@ -9214,8 +9327,13 @@
         <x:f>IF(ISNUMBER(J25),IF(J25&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L25" s="1"/>
-      <x:c r="M25" s="1"/>
+      <x:c r="L25" s="19" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="M25" s="18" t="str">
+        <x:f>IF(ISNUMBER(L25),IF(L25&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N25" s="1"/>
       <x:c r="O25" s="1"/>
     </x:row>
@@ -9254,8 +9372,13 @@
         <x:f>IF(ISNUMBER(J26),IF(J26&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L26" s="1"/>
-      <x:c r="M26" s="1"/>
+      <x:c r="L26" s="19" t="n">
+        <x:v>9.7</x:v>
+      </x:c>
+      <x:c r="M26" s="18" t="str">
+        <x:f>IF(ISNUMBER(L26),IF(L26&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N26" s="1"/>
       <x:c r="O26" s="1"/>
     </x:row>
@@ -9294,8 +9417,13 @@
         <x:f>IF(ISNUMBER(J27),IF(J27&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L27" s="1"/>
-      <x:c r="M27" s="1"/>
+      <x:c r="L27" s="19" t="n">
+        <x:v>28.4</x:v>
+      </x:c>
+      <x:c r="M27" s="18" t="str">
+        <x:f>IF(ISNUMBER(L27),IF(L27&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N27" s="1"/>
       <x:c r="O27" s="1"/>
     </x:row>
@@ -9334,8 +9462,13 @@
         <x:f>IF(ISNUMBER(J28),IF(J28&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L28" s="1"/>
-      <x:c r="M28" s="1"/>
+      <x:c r="L28" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="M28" s="18" t="str">
+        <x:f>IF(ISNUMBER(L28),IF(L28&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N28" s="1"/>
       <x:c r="O28" s="1"/>
     </x:row>
@@ -9374,8 +9507,13 @@
         <x:f>IF(ISNUMBER(J29),IF(J29&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L29" s="1"/>
-      <x:c r="M29" s="1"/>
+      <x:c r="L29" s="19" t="n">
+        <x:v>-12.7</x:v>
+      </x:c>
+      <x:c r="M29" s="18" t="str">
+        <x:f>IF(ISNUMBER(L29),IF(L29&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N29" s="1"/>
       <x:c r="O29" s="1"/>
     </x:row>
@@ -9414,8 +9552,13 @@
         <x:f>IF(ISNUMBER(J30),IF(J30&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L30" s="1"/>
-      <x:c r="M30" s="1"/>
+      <x:c r="L30" s="19" t="n">
+        <x:v>-1.1</x:v>
+      </x:c>
+      <x:c r="M30" s="18" t="str">
+        <x:f>IF(ISNUMBER(L30),IF(L30&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N30" s="1"/>
       <x:c r="O30" s="1"/>
     </x:row>
@@ -9454,8 +9597,13 @@
         <x:f>IF(ISNUMBER(J31),IF(J31&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L31" s="1"/>
-      <x:c r="M31" s="1"/>
+      <x:c r="L31" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M31" s="18" t="str">
+        <x:f>IF(ISNUMBER(L31),IF(L31&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N31" s="1"/>
       <x:c r="O31" s="1"/>
     </x:row>
@@ -9494,8 +9642,13 @@
         <x:f>IF(ISNUMBER(J32),IF(J32&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L32" s="1"/>
-      <x:c r="M32" s="1"/>
+      <x:c r="L32" s="19" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="M32" s="18" t="str">
+        <x:f>IF(ISNUMBER(L32),IF(L32&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N32" s="1"/>
       <x:c r="O32" s="1"/>
     </x:row>
@@ -9534,8 +9687,13 @@
         <x:f>IF(ISNUMBER(J33),IF(J33&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L33" s="1"/>
-      <x:c r="M33" s="1"/>
+      <x:c r="L33" s="19" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="M33" s="18" t="str">
+        <x:f>IF(ISNUMBER(L33),IF(L33&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N33" s="1"/>
       <x:c r="O33" s="1"/>
     </x:row>
@@ -9574,8 +9732,13 @@
         <x:f>IF(ISNUMBER(J34),IF(J34&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L34" s="1"/>
-      <x:c r="M34" s="1"/>
+      <x:c r="L34" s="19" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="M34" s="18" t="str">
+        <x:f>IF(ISNUMBER(L34),IF(L34&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N34" s="1"/>
       <x:c r="O34" s="1"/>
     </x:row>
@@ -9614,8 +9777,13 @@
         <x:f>IF(ISNUMBER(J35),IF(J35&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L35" s="1"/>
-      <x:c r="M35" s="1"/>
+      <x:c r="L35" s="19" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="M35" s="18" t="str">
+        <x:f>IF(ISNUMBER(L35),IF(L35&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N35" s="1"/>
       <x:c r="O35" s="1"/>
     </x:row>
@@ -9654,8 +9822,13 @@
         <x:f>IF(ISNUMBER(J36),IF(J36&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L36" s="1"/>
-      <x:c r="M36" s="1"/>
+      <x:c r="L36" s="19" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="M36" s="18" t="str">
+        <x:f>IF(ISNUMBER(L36),IF(L36&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N36" s="1"/>
       <x:c r="O36" s="1"/>
     </x:row>
@@ -9694,8 +9867,13 @@
         <x:f>IF(ISNUMBER(J37),IF(J37&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L37" s="1"/>
-      <x:c r="M37" s="1"/>
+      <x:c r="L37" s="19" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="M37" s="18" t="str">
+        <x:f>IF(ISNUMBER(L37),IF(L37&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N37" s="1"/>
       <x:c r="O37" s="1"/>
     </x:row>
@@ -9734,8 +9912,13 @@
         <x:f>IF(ISNUMBER(J38),IF(J38&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L38" s="1"/>
-      <x:c r="M38" s="1"/>
+      <x:c r="L38" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="M38" s="18" t="str">
+        <x:f>IF(ISNUMBER(L38),IF(L38&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N38" s="1"/>
       <x:c r="O38" s="1"/>
     </x:row>
@@ -9774,8 +9957,13 @@
         <x:f>IF(ISNUMBER(J39),IF(J39&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L39" s="1"/>
-      <x:c r="M39" s="1"/>
+      <x:c r="L39" s="19" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="M39" s="18" t="str">
+        <x:f>IF(ISNUMBER(L39),IF(L39&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N39" s="1"/>
       <x:c r="O39" s="1"/>
     </x:row>
@@ -9814,8 +10002,13 @@
         <x:f>IF(ISNUMBER(J40),IF(J40&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L40" s="1"/>
-      <x:c r="M40" s="1"/>
+      <x:c r="L40" s="19" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="M40" s="18" t="str">
+        <x:f>IF(ISNUMBER(L40),IF(L40&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N40" s="1"/>
       <x:c r="O40" s="1"/>
     </x:row>
@@ -9854,8 +10047,13 @@
         <x:f>IF(ISNUMBER(J41),IF(J41&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L41" s="1"/>
-      <x:c r="M41" s="1"/>
+      <x:c r="L41" s="19" t="n">
+        <x:v>-1.3</x:v>
+      </x:c>
+      <x:c r="M41" s="18" t="str">
+        <x:f>IF(ISNUMBER(L41),IF(L41&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N41" s="1"/>
       <x:c r="O41" s="1"/>
     </x:row>
@@ -9894,8 +10092,13 @@
         <x:f>IF(ISNUMBER(J42),IF(J42&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L42" s="1"/>
-      <x:c r="M42" s="1"/>
+      <x:c r="L42" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M42" s="18" t="str">
+        <x:f>IF(ISNUMBER(L42),IF(L42&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N42" s="1"/>
       <x:c r="O42" s="1"/>
     </x:row>
@@ -9934,8 +10137,13 @@
         <x:f>IF(ISNUMBER(J43),IF(J43&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L43" s="1"/>
-      <x:c r="M43" s="1"/>
+      <x:c r="L43" s="19" t="n">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="M43" s="18" t="str">
+        <x:f>IF(ISNUMBER(L43),IF(L43&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N43" s="1"/>
       <x:c r="O43" s="1"/>
     </x:row>
@@ -9974,8 +10182,13 @@
         <x:f>IF(ISNUMBER(J44),IF(J44&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L44" s="1"/>
-      <x:c r="M44" s="1"/>
+      <x:c r="L44" s="19" t="n">
+        <x:v>-3.9</x:v>
+      </x:c>
+      <x:c r="M44" s="18" t="str">
+        <x:f>IF(ISNUMBER(L44),IF(L44&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N44" s="1"/>
       <x:c r="O44" s="1"/>
     </x:row>
@@ -10014,8 +10227,13 @@
         <x:f>IF(ISNUMBER(J45),IF(J45&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L45" s="1"/>
-      <x:c r="M45" s="1"/>
+      <x:c r="L45" s="19" t="n">
+        <x:v>-0.6</x:v>
+      </x:c>
+      <x:c r="M45" s="18" t="str">
+        <x:f>IF(ISNUMBER(L45),IF(L45&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N45" s="1"/>
       <x:c r="O45" s="1"/>
     </x:row>
@@ -10054,8 +10272,13 @@
         <x:f>IF(ISNUMBER(J46),IF(J46&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L46" s="1"/>
-      <x:c r="M46" s="1"/>
+      <x:c r="L46" s="19" t="n">
+        <x:v>8.4</x:v>
+      </x:c>
+      <x:c r="M46" s="18" t="str">
+        <x:f>IF(ISNUMBER(L46),IF(L46&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N46" s="1"/>
       <x:c r="O46" s="1"/>
     </x:row>
@@ -10094,8 +10317,13 @@
         <x:f>IF(ISNUMBER(J47),IF(J47&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L47" s="1"/>
-      <x:c r="M47" s="1"/>
+      <x:c r="L47" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M47" s="18" t="str">
+        <x:f>IF(ISNUMBER(L47),IF(L47&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N47" s="1"/>
       <x:c r="O47" s="1"/>
     </x:row>
@@ -10134,8 +10362,13 @@
         <x:f>IF(ISNUMBER(J48),IF(J48&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L48" s="1"/>
-      <x:c r="M48" s="1"/>
+      <x:c r="L48" s="19" t="n">
+        <x:v>8.2</x:v>
+      </x:c>
+      <x:c r="M48" s="18" t="str">
+        <x:f>IF(ISNUMBER(L48),IF(L48&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N48" s="1"/>
       <x:c r="O48" s="1"/>
     </x:row>
@@ -10174,8 +10407,13 @@
         <x:f>IF(ISNUMBER(J49),IF(J49&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L49" s="1"/>
-      <x:c r="M49" s="1"/>
+      <x:c r="L49" s="19" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="M49" s="18" t="str">
+        <x:f>IF(ISNUMBER(L49),IF(L49&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N49" s="1"/>
       <x:c r="O49" s="1"/>
     </x:row>
@@ -10214,8 +10452,13 @@
         <x:f>IF(ISNUMBER(J50),IF(J50&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L50" s="1"/>
-      <x:c r="M50" s="1"/>
+      <x:c r="L50" s="19" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="M50" s="18" t="str">
+        <x:f>IF(ISNUMBER(L50),IF(L50&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N50" s="1"/>
       <x:c r="O50" s="1"/>
     </x:row>
@@ -10254,8 +10497,13 @@
         <x:f>IF(ISNUMBER(J51),IF(J51&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L51" s="1"/>
-      <x:c r="M51" s="1"/>
+      <x:c r="L51" s="19" t="n">
+        <x:v>-2.4</x:v>
+      </x:c>
+      <x:c r="M51" s="18" t="str">
+        <x:f>IF(ISNUMBER(L51),IF(L51&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N51" s="1"/>
       <x:c r="O51" s="1"/>
     </x:row>
@@ -10294,8 +10542,13 @@
         <x:f>IF(ISNUMBER(J52),IF(J52&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L52" s="1"/>
-      <x:c r="M52" s="1"/>
+      <x:c r="L52" s="19" t="n">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="M52" s="18" t="str">
+        <x:f>IF(ISNUMBER(L52),IF(L52&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N52" s="1"/>
       <x:c r="O52" s="1"/>
     </x:row>
@@ -10334,8 +10587,13 @@
         <x:f>IF(ISNUMBER(J53),IF(J53&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L53" s="1"/>
-      <x:c r="M53" s="1"/>
+      <x:c r="L53" s="19" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="M53" s="18" t="str">
+        <x:f>IF(ISNUMBER(L53),IF(L53&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N53" s="1"/>
       <x:c r="O53" s="1"/>
     </x:row>
@@ -10374,8 +10632,13 @@
         <x:f>IF(ISNUMBER(J54),IF(J54&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L54" s="1"/>
-      <x:c r="M54" s="1"/>
+      <x:c r="L54" s="19" t="n">
+        <x:v>-0.8</x:v>
+      </x:c>
+      <x:c r="M54" s="18" t="str">
+        <x:f>IF(ISNUMBER(L54),IF(L54&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N54" s="1"/>
       <x:c r="O54" s="1"/>
     </x:row>
@@ -10414,8 +10677,13 @@
         <x:f>IF(ISNUMBER(J55),IF(J55&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L55" s="1"/>
-      <x:c r="M55" s="1"/>
+      <x:c r="L55" s="19" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="M55" s="18" t="str">
+        <x:f>IF(ISNUMBER(L55),IF(L55&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N55" s="1"/>
       <x:c r="O55" s="1"/>
     </x:row>
@@ -10454,8 +10722,13 @@
         <x:f>IF(ISNUMBER(J56),IF(J56&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L56" s="1"/>
-      <x:c r="M56" s="1"/>
+      <x:c r="L56" s="19" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="M56" s="18" t="str">
+        <x:f>IF(ISNUMBER(L56),IF(L56&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N56" s="1"/>
       <x:c r="O56" s="1"/>
     </x:row>
@@ -10494,8 +10767,13 @@
         <x:f>IF(ISNUMBER(J57),IF(J57&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L57" s="1"/>
-      <x:c r="M57" s="1"/>
+      <x:c r="L57" s="19" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="M57" s="18" t="str">
+        <x:f>IF(ISNUMBER(L57),IF(L57&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N57" s="1"/>
       <x:c r="O57" s="1"/>
     </x:row>
@@ -10534,8 +10812,13 @@
         <x:f>IF(ISNUMBER(J58),IF(J58&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L58" s="1"/>
-      <x:c r="M58" s="1"/>
+      <x:c r="L58" s="19" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="M58" s="18" t="str">
+        <x:f>IF(ISNUMBER(L58),IF(L58&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N58" s="1"/>
       <x:c r="O58" s="1"/>
     </x:row>
@@ -10574,8 +10857,13 @@
         <x:f>IF(ISNUMBER(J59),IF(J59&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L59" s="1"/>
-      <x:c r="M59" s="1"/>
+      <x:c r="L59" s="19" t="n">
+        <x:v>6.8</x:v>
+      </x:c>
+      <x:c r="M59" s="18" t="str">
+        <x:f>IF(ISNUMBER(L59),IF(L59&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N59" s="1"/>
       <x:c r="O59" s="1"/>
     </x:row>
@@ -10614,8 +10902,13 @@
         <x:f>IF(ISNUMBER(J60),IF(J60&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L60" s="1"/>
-      <x:c r="M60" s="1"/>
+      <x:c r="L60" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M60" s="18" t="str">
+        <x:f>IF(ISNUMBER(L60),IF(L60&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N60" s="1"/>
       <x:c r="O60" s="1"/>
     </x:row>
@@ -10654,8 +10947,13 @@
         <x:f>IF(ISNUMBER(J61),IF(J61&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L61" s="1"/>
-      <x:c r="M61" s="1"/>
+      <x:c r="L61" s="19" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="M61" s="18" t="str">
+        <x:f>IF(ISNUMBER(L61),IF(L61&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N61" s="1"/>
       <x:c r="O61" s="1"/>
     </x:row>
@@ -10694,8 +10992,13 @@
         <x:f>IF(ISNUMBER(J62),IF(J62&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L62" s="1"/>
-      <x:c r="M62" s="1"/>
+      <x:c r="L62" s="19" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="M62" s="18" t="str">
+        <x:f>IF(ISNUMBER(L62),IF(L62&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N62" s="1"/>
       <x:c r="O62" s="1"/>
     </x:row>
@@ -10734,8 +11037,13 @@
         <x:f>IF(ISNUMBER(J63),IF(J63&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L63" s="1"/>
-      <x:c r="M63" s="1"/>
+      <x:c r="L63" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M63" s="18" t="str">
+        <x:f>IF(ISNUMBER(L63),IF(L63&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N63" s="1"/>
       <x:c r="O63" s="1"/>
     </x:row>
@@ -10774,8 +11082,13 @@
         <x:f>IF(ISNUMBER(J64),IF(J64&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L64" s="1"/>
-      <x:c r="M64" s="1"/>
+      <x:c r="L64" s="19" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="M64" s="18" t="str">
+        <x:f>IF(ISNUMBER(L64),IF(L64&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N64" s="1"/>
       <x:c r="O64" s="1"/>
     </x:row>
@@ -10814,8 +11127,13 @@
         <x:f>IF(ISNUMBER(J65),IF(J65&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L65" s="1"/>
-      <x:c r="M65" s="1"/>
+      <x:c r="L65" s="19" t="n">
+        <x:v>-3.9</x:v>
+      </x:c>
+      <x:c r="M65" s="18" t="str">
+        <x:f>IF(ISNUMBER(L65),IF(L65&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N65" s="1"/>
       <x:c r="O65" s="1"/>
     </x:row>
@@ -10854,8 +11172,13 @@
         <x:f>IF(ISNUMBER(J66),IF(J66&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L66" s="1"/>
-      <x:c r="M66" s="1"/>
+      <x:c r="L66" s="19" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="M66" s="18" t="str">
+        <x:f>IF(ISNUMBER(L66),IF(L66&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N66" s="1"/>
       <x:c r="O66" s="1"/>
     </x:row>
@@ -10894,8 +11217,13 @@
         <x:f>IF(ISNUMBER(J67),IF(J67&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L67" s="1"/>
-      <x:c r="M67" s="1"/>
+      <x:c r="L67" s="19" t="n">
+        <x:v>7.1</x:v>
+      </x:c>
+      <x:c r="M67" s="18" t="str">
+        <x:f>IF(ISNUMBER(L67),IF(L67&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N67" s="1"/>
       <x:c r="O67" s="1"/>
     </x:row>
@@ -10934,8 +11262,13 @@
         <x:f>IF(ISNUMBER(J68),IF(J68&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L68" s="1"/>
-      <x:c r="M68" s="1"/>
+      <x:c r="L68" s="19" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="M68" s="18" t="str">
+        <x:f>IF(ISNUMBER(L68),IF(L68&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N68" s="1"/>
       <x:c r="O68" s="1"/>
     </x:row>
@@ -10974,8 +11307,13 @@
         <x:f>IF(ISNUMBER(J69),IF(J69&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L69" s="1"/>
-      <x:c r="M69" s="1"/>
+      <x:c r="L69" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="M69" s="18" t="str">
+        <x:f>IF(ISNUMBER(L69),IF(L69&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N69" s="1"/>
       <x:c r="O69" s="1"/>
     </x:row>
@@ -11014,8 +11352,13 @@
         <x:f>IF(ISNUMBER(J70),IF(J70&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L70" s="1"/>
-      <x:c r="M70" s="1"/>
+      <x:c r="L70" s="19" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="M70" s="18" t="str">
+        <x:f>IF(ISNUMBER(L70),IF(L70&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N70" s="1"/>
       <x:c r="O70" s="1"/>
     </x:row>
@@ -11054,8 +11397,13 @@
         <x:f>IF(ISNUMBER(J71),IF(J71&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L71" s="1"/>
-      <x:c r="M71" s="1"/>
+      <x:c r="L71" s="19" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="M71" s="18" t="str">
+        <x:f>IF(ISNUMBER(L71),IF(L71&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N71" s="1"/>
       <x:c r="O71" s="1"/>
     </x:row>
@@ -11094,8 +11442,13 @@
         <x:f>IF(ISNUMBER(J72),IF(J72&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L72" s="1"/>
-      <x:c r="M72" s="1"/>
+      <x:c r="L72" s="19" t="n">
+        <x:v>-7.6</x:v>
+      </x:c>
+      <x:c r="M72" s="18" t="str">
+        <x:f>IF(ISNUMBER(L72),IF(L72&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N72" s="1"/>
       <x:c r="O72" s="1"/>
     </x:row>
@@ -11134,8 +11487,13 @@
         <x:f>IF(ISNUMBER(J73),IF(J73&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L73" s="1"/>
-      <x:c r="M73" s="1"/>
+      <x:c r="L73" s="19" t="n">
+        <x:v>-1.2</x:v>
+      </x:c>
+      <x:c r="M73" s="18" t="str">
+        <x:f>IF(ISNUMBER(L73),IF(L73&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N73" s="1"/>
       <x:c r="O73" s="1"/>
     </x:row>
@@ -11174,8 +11532,13 @@
         <x:f>IF(ISNUMBER(J74),IF(J74&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L74" s="1"/>
-      <x:c r="M74" s="1"/>
+      <x:c r="L74" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M74" s="18" t="str">
+        <x:f>IF(ISNUMBER(L74),IF(L74&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N74" s="1"/>
       <x:c r="O74" s="1"/>
     </x:row>
@@ -11214,8 +11577,13 @@
         <x:f>IF(ISNUMBER(J75),IF(J75&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L75" s="1"/>
-      <x:c r="M75" s="1"/>
+      <x:c r="L75" s="19" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="M75" s="18" t="str">
+        <x:f>IF(ISNUMBER(L75),IF(L75&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N75" s="1"/>
       <x:c r="O75" s="1"/>
     </x:row>
@@ -11254,8 +11622,13 @@
         <x:f>IF(ISNUMBER(J76),IF(J76&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L76" s="1"/>
-      <x:c r="M76" s="1"/>
+      <x:c r="L76" s="19" t="n">
+        <x:v>-0.8</x:v>
+      </x:c>
+      <x:c r="M76" s="18" t="str">
+        <x:f>IF(ISNUMBER(L76),IF(L76&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N76" s="1"/>
       <x:c r="O76" s="1"/>
     </x:row>
@@ -11294,8 +11667,13 @@
         <x:f>IF(ISNUMBER(J77),IF(J77&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L77" s="1"/>
-      <x:c r="M77" s="1"/>
+      <x:c r="L77" s="19" t="n">
+        <x:v>-0.3</x:v>
+      </x:c>
+      <x:c r="M77" s="18" t="str">
+        <x:f>IF(ISNUMBER(L77),IF(L77&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N77" s="1"/>
       <x:c r="O77" s="1"/>
     </x:row>
@@ -11334,8 +11712,13 @@
         <x:f>IF(ISNUMBER(J78),IF(J78&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L78" s="1"/>
-      <x:c r="M78" s="1"/>
+      <x:c r="L78" s="19" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="M78" s="18" t="str">
+        <x:f>IF(ISNUMBER(L78),IF(L78&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N78" s="1"/>
       <x:c r="O78" s="1"/>
     </x:row>
@@ -11374,8 +11757,13 @@
         <x:f>IF(ISNUMBER(J79),IF(J79&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L79" s="1"/>
-      <x:c r="M79" s="1"/>
+      <x:c r="L79" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="M79" s="18" t="str">
+        <x:f>IF(ISNUMBER(L79),IF(L79&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N79" s="1"/>
       <x:c r="O79" s="1"/>
     </x:row>
@@ -11414,8 +11802,13 @@
         <x:f>IF(ISNUMBER(J80),IF(J80&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L80" s="1"/>
-      <x:c r="M80" s="1"/>
+      <x:c r="L80" s="19" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="M80" s="18" t="str">
+        <x:f>IF(ISNUMBER(L80),IF(L80&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N80" s="1"/>
       <x:c r="O80" s="1"/>
     </x:row>
@@ -11454,8 +11847,13 @@
         <x:f>IF(ISNUMBER(J81),IF(J81&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L81" s="1"/>
-      <x:c r="M81" s="1"/>
+      <x:c r="L81" s="19" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="M81" s="18" t="str">
+        <x:f>IF(ISNUMBER(L81),IF(L81&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N81" s="1"/>
       <x:c r="O81" s="1"/>
     </x:row>
@@ -11494,8 +11892,13 @@
         <x:f>IF(ISNUMBER(J82),IF(J82&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L82" s="1"/>
-      <x:c r="M82" s="1"/>
+      <x:c r="L82" s="19" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="M82" s="18" t="str">
+        <x:f>IF(ISNUMBER(L82),IF(L82&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N82" s="1"/>
       <x:c r="O82" s="1"/>
     </x:row>
@@ -11534,8 +11937,13 @@
         <x:f>IF(ISNUMBER(J83),IF(J83&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L83" s="1"/>
-      <x:c r="M83" s="1"/>
+      <x:c r="L83" s="19" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="M83" s="18" t="str">
+        <x:f>IF(ISNUMBER(L83),IF(L83&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N83" s="1"/>
       <x:c r="O83" s="1"/>
     </x:row>
@@ -11574,8 +11982,13 @@
         <x:f>IF(ISNUMBER(J84),IF(J84&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L84" s="1"/>
-      <x:c r="M84" s="1"/>
+      <x:c r="L84" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M84" s="18" t="str">
+        <x:f>IF(ISNUMBER(L84),IF(L84&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N84" s="1"/>
       <x:c r="O84" s="1"/>
     </x:row>
@@ -11614,8 +12027,13 @@
         <x:f>IF(ISNUMBER(J85),IF(J85&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L85" s="1"/>
-      <x:c r="M85" s="1"/>
+      <x:c r="L85" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M85" s="18" t="str">
+        <x:f>IF(ISNUMBER(L85),IF(L85&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N85" s="1"/>
       <x:c r="O85" s="1"/>
     </x:row>
@@ -11654,8 +12072,13 @@
         <x:f>IF(ISNUMBER(J86),IF(J86&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L86" s="1"/>
-      <x:c r="M86" s="1"/>
+      <x:c r="L86" s="19" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="M86" s="18" t="str">
+        <x:f>IF(ISNUMBER(L86),IF(L86&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N86" s="1"/>
       <x:c r="O86" s="1"/>
     </x:row>
@@ -11694,8 +12117,13 @@
         <x:f>IF(ISNUMBER(J87),IF(J87&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L87" s="1"/>
-      <x:c r="M87" s="1"/>
+      <x:c r="L87" s="19" t="n">
+        <x:v>-1.2</x:v>
+      </x:c>
+      <x:c r="M87" s="18" t="str">
+        <x:f>IF(ISNUMBER(L87),IF(L87&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N87" s="1"/>
       <x:c r="O87" s="1"/>
     </x:row>
@@ -11734,8 +12162,13 @@
         <x:f>IF(ISNUMBER(J88),IF(J88&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L88" s="1"/>
-      <x:c r="M88" s="1"/>
+      <x:c r="L88" s="19" t="n">
+        <x:v>-0.7</x:v>
+      </x:c>
+      <x:c r="M88" s="18" t="str">
+        <x:f>IF(ISNUMBER(L88),IF(L88&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N88" s="1"/>
       <x:c r="O88" s="1"/>
     </x:row>
@@ -11774,8 +12207,13 @@
         <x:f>IF(ISNUMBER(J89),IF(J89&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L89" s="1"/>
-      <x:c r="M89" s="1"/>
+      <x:c r="L89" s="19" t="n">
+        <x:v>7.4</x:v>
+      </x:c>
+      <x:c r="M89" s="18" t="str">
+        <x:f>IF(ISNUMBER(L89),IF(L89&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N89" s="1"/>
       <x:c r="O89" s="1"/>
     </x:row>
@@ -11814,8 +12252,13 @@
         <x:f>IF(ISNUMBER(J90),IF(J90&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L90" s="1"/>
-      <x:c r="M90" s="1"/>
+      <x:c r="L90" s="19" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="M90" s="18" t="str">
+        <x:f>IF(ISNUMBER(L90),IF(L90&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N90" s="1"/>
       <x:c r="O90" s="1"/>
     </x:row>
@@ -11854,8 +12297,13 @@
         <x:f>IF(ISNUMBER(J91),IF(J91&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L91" s="1"/>
-      <x:c r="M91" s="1"/>
+      <x:c r="L91" s="19" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="M91" s="18" t="str">
+        <x:f>IF(ISNUMBER(L91),IF(L91&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N91" s="1"/>
       <x:c r="O91" s="1"/>
     </x:row>
@@ -11894,8 +12342,13 @@
         <x:f>IF(ISNUMBER(J92),IF(J92&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L92" s="1"/>
-      <x:c r="M92" s="1"/>
+      <x:c r="L92" s="19" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="M92" s="18" t="str">
+        <x:f>IF(ISNUMBER(L92),IF(L92&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N92" s="1"/>
       <x:c r="O92" s="1"/>
     </x:row>
@@ -11934,8 +12387,13 @@
         <x:f>IF(ISNUMBER(J93),IF(J93&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L93" s="1"/>
-      <x:c r="M93" s="1"/>
+      <x:c r="L93" s="19" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="M93" s="18" t="str">
+        <x:f>IF(ISNUMBER(L93),IF(L93&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N93" s="1"/>
       <x:c r="O93" s="1"/>
     </x:row>
@@ -11974,8 +12432,13 @@
         <x:f>IF(ISNUMBER(J94),IF(J94&gt;3,"是","否"),"跳过")</x:f>
         <x:v>跳过</x:v>
       </x:c>
-      <x:c r="L94" s="1"/>
-      <x:c r="M94" s="1"/>
+      <x:c r="L94" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M94" s="18" t="str">
+        <x:f>IF(ISNUMBER(L94),IF(L94&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>跳过</x:v>
+      </x:c>
       <x:c r="N94" s="1"/>
       <x:c r="O94" s="1"/>
     </x:row>
@@ -12014,8 +12477,13 @@
         <x:f>IF(ISNUMBER(J95),IF(J95&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L95" s="1"/>
-      <x:c r="M95" s="1"/>
+      <x:c r="L95" s="19" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="M95" s="18" t="str">
+        <x:f>IF(ISNUMBER(L95),IF(L95&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N95" s="1"/>
       <x:c r="O95" s="1"/>
     </x:row>
@@ -12054,8 +12522,13 @@
         <x:f>IF(ISNUMBER(J96),IF(J96&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L96" s="1"/>
-      <x:c r="M96" s="1"/>
+      <x:c r="L96" s="19" t="n">
+        <x:v>5.3</x:v>
+      </x:c>
+      <x:c r="M96" s="18" t="str">
+        <x:f>IF(ISNUMBER(L96),IF(L96&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N96" s="1"/>
       <x:c r="O96" s="1"/>
     </x:row>
@@ -12094,8 +12567,13 @@
         <x:f>IF(ISNUMBER(J97),IF(J97&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L97" s="1"/>
-      <x:c r="M97" s="1"/>
+      <x:c r="L97" s="19" t="n">
+        <x:v>6.4</x:v>
+      </x:c>
+      <x:c r="M97" s="18" t="str">
+        <x:f>IF(ISNUMBER(L97),IF(L97&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N97" s="1"/>
       <x:c r="O97" s="1"/>
     </x:row>
@@ -12134,8 +12612,13 @@
         <x:f>IF(ISNUMBER(J98),IF(J98&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L98" s="1"/>
-      <x:c r="M98" s="1"/>
+      <x:c r="L98" s="19" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="M98" s="18" t="str">
+        <x:f>IF(ISNUMBER(L98),IF(L98&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N98" s="1"/>
       <x:c r="O98" s="1"/>
     </x:row>
@@ -12174,8 +12657,13 @@
         <x:f>IF(ISNUMBER(J99),IF(J99&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L99" s="1"/>
-      <x:c r="M99" s="1"/>
+      <x:c r="L99" s="19" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="M99" s="18" t="str">
+        <x:f>IF(ISNUMBER(L99),IF(L99&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N99" s="1"/>
       <x:c r="O99" s="1"/>
     </x:row>
@@ -12214,8 +12702,13 @@
         <x:f>IF(ISNUMBER(J100),IF(J100&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L100" s="1"/>
-      <x:c r="M100" s="1"/>
+      <x:c r="L100" s="19" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="M100" s="18" t="str">
+        <x:f>IF(ISNUMBER(L100),IF(L100&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N100" s="1"/>
       <x:c r="O100" s="1"/>
     </x:row>
@@ -12254,8 +12747,13 @@
         <x:f>IF(ISNUMBER(J101),IF(J101&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L101" s="1"/>
-      <x:c r="M101" s="1"/>
+      <x:c r="L101" s="19" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="M101" s="18" t="str">
+        <x:f>IF(ISNUMBER(L101),IF(L101&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N101" s="1"/>
       <x:c r="O101" s="1"/>
     </x:row>
@@ -12294,8 +12792,13 @@
         <x:f>IF(ISNUMBER(J102),IF(J102&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L102" s="1"/>
-      <x:c r="M102" s="1"/>
+      <x:c r="L102" s="19" t="n">
+        <x:v>74.2</x:v>
+      </x:c>
+      <x:c r="M102" s="18" t="str">
+        <x:f>IF(ISNUMBER(L102),IF(L102&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N102" s="1"/>
       <x:c r="O102" s="1"/>
     </x:row>
@@ -12334,8 +12837,13 @@
         <x:f>IF(ISNUMBER(J103),IF(J103&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L103" s="1"/>
-      <x:c r="M103" s="1"/>
+      <x:c r="L103" s="19" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="M103" s="18" t="str">
+        <x:f>IF(ISNUMBER(L103),IF(L103&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N103" s="1"/>
       <x:c r="O103" s="1"/>
     </x:row>
@@ -12374,8 +12882,13 @@
         <x:f>IF(ISNUMBER(J104),IF(J104&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L104" s="1"/>
-      <x:c r="M104" s="1"/>
+      <x:c r="L104" s="19" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="M104" s="18" t="str">
+        <x:f>IF(ISNUMBER(L104),IF(L104&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N104" s="1"/>
       <x:c r="O104" s="1"/>
     </x:row>
@@ -12414,8 +12927,13 @@
         <x:f>IF(ISNUMBER(J105),IF(J105&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L105" s="1"/>
-      <x:c r="M105" s="1"/>
+      <x:c r="L105" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M105" s="18" t="str">
+        <x:f>IF(ISNUMBER(L105),IF(L105&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N105" s="1"/>
       <x:c r="O105" s="1"/>
     </x:row>
@@ -12454,8 +12972,13 @@
         <x:f>IF(ISNUMBER(J106),IF(J106&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L106" s="1"/>
-      <x:c r="M106" s="1"/>
+      <x:c r="L106" s="19" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="M106" s="18" t="str">
+        <x:f>IF(ISNUMBER(L106),IF(L106&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N106" s="1"/>
       <x:c r="O106" s="1"/>
     </x:row>
@@ -12494,8 +13017,13 @@
         <x:f>IF(ISNUMBER(J107),IF(J107&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L107" s="1"/>
-      <x:c r="M107" s="1"/>
+      <x:c r="L107" s="19" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="M107" s="18" t="str">
+        <x:f>IF(ISNUMBER(L107),IF(L107&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N107" s="1"/>
       <x:c r="O107" s="1"/>
     </x:row>
@@ -12534,8 +13062,13 @@
         <x:f>IF(ISNUMBER(J108),IF(J108&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L108" s="1"/>
-      <x:c r="M108" s="1"/>
+      <x:c r="L108" s="19" t="n">
+        <x:v>-0.7</x:v>
+      </x:c>
+      <x:c r="M108" s="18" t="str">
+        <x:f>IF(ISNUMBER(L108),IF(L108&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N108" s="1"/>
       <x:c r="O108" s="1"/>
     </x:row>
@@ -12574,8 +13107,13 @@
         <x:f>IF(ISNUMBER(J109),IF(J109&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L109" s="1"/>
-      <x:c r="M109" s="1"/>
+      <x:c r="L109" s="19" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="M109" s="18" t="str">
+        <x:f>IF(ISNUMBER(L109),IF(L109&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N109" s="1"/>
       <x:c r="O109" s="1"/>
     </x:row>
@@ -12614,8 +13152,13 @@
         <x:f>IF(ISNUMBER(J110),IF(J110&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L110" s="1"/>
-      <x:c r="M110" s="1"/>
+      <x:c r="L110" s="19" t="n">
+        <x:v>-3.5</x:v>
+      </x:c>
+      <x:c r="M110" s="18" t="str">
+        <x:f>IF(ISNUMBER(L110),IF(L110&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N110" s="1"/>
       <x:c r="O110" s="1"/>
     </x:row>
@@ -12654,8 +13197,13 @@
         <x:f>IF(ISNUMBER(J111),IF(J111&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L111" s="1"/>
-      <x:c r="M111" s="1"/>
+      <x:c r="L111" s="19" t="n">
+        <x:v>-3.7</x:v>
+      </x:c>
+      <x:c r="M111" s="18" t="str">
+        <x:f>IF(ISNUMBER(L111),IF(L111&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N111" s="1"/>
       <x:c r="O111" s="1"/>
     </x:row>
@@ -12694,8 +13242,13 @@
         <x:f>IF(ISNUMBER(J112),IF(J112&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L112" s="1"/>
-      <x:c r="M112" s="1"/>
+      <x:c r="L112" s="19" t="n">
+        <x:v>-0.7</x:v>
+      </x:c>
+      <x:c r="M112" s="18" t="str">
+        <x:f>IF(ISNUMBER(L112),IF(L112&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N112" s="1"/>
       <x:c r="O112" s="1"/>
     </x:row>
@@ -12734,8 +13287,13 @@
         <x:f>IF(ISNUMBER(J113),IF(J113&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L113" s="1"/>
-      <x:c r="M113" s="1"/>
+      <x:c r="L113" s="19" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="M113" s="18" t="str">
+        <x:f>IF(ISNUMBER(L113),IF(L113&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N113" s="1"/>
       <x:c r="O113" s="1"/>
     </x:row>
@@ -12774,8 +13332,13 @@
         <x:f>IF(ISNUMBER(J114),IF(J114&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L114" s="1"/>
-      <x:c r="M114" s="1"/>
+      <x:c r="L114" s="19" t="n">
+        <x:v>-2.3</x:v>
+      </x:c>
+      <x:c r="M114" s="18" t="str">
+        <x:f>IF(ISNUMBER(L114),IF(L114&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N114" s="1"/>
       <x:c r="O114" s="1"/>
     </x:row>
@@ -12814,8 +13377,13 @@
         <x:f>IF(ISNUMBER(J115),IF(J115&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L115" s="1"/>
-      <x:c r="M115" s="1"/>
+      <x:c r="L115" s="19" t="n">
+        <x:v>-0.3</x:v>
+      </x:c>
+      <x:c r="M115" s="18" t="str">
+        <x:f>IF(ISNUMBER(L115),IF(L115&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N115" s="1"/>
       <x:c r="O115" s="1"/>
     </x:row>
@@ -12854,8 +13422,13 @@
         <x:f>IF(ISNUMBER(J116),IF(J116&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L116" s="1"/>
-      <x:c r="M116" s="1"/>
+      <x:c r="L116" s="19" t="n">
+        <x:v>-1.1</x:v>
+      </x:c>
+      <x:c r="M116" s="18" t="str">
+        <x:f>IF(ISNUMBER(L116),IF(L116&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N116" s="1"/>
       <x:c r="O116" s="1"/>
     </x:row>
@@ -12894,8 +13467,13 @@
         <x:f>IF(ISNUMBER(J117),IF(J117&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L117" s="1"/>
-      <x:c r="M117" s="1"/>
+      <x:c r="L117" s="19" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="M117" s="18" t="str">
+        <x:f>IF(ISNUMBER(L117),IF(L117&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N117" s="1"/>
       <x:c r="O117" s="1"/>
     </x:row>
@@ -12934,8 +13512,13 @@
         <x:f>IF(ISNUMBER(J118),IF(J118&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L118" s="1"/>
-      <x:c r="M118" s="1"/>
+      <x:c r="L118" s="19" t="n">
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="M118" s="18" t="str">
+        <x:f>IF(ISNUMBER(L118),IF(L118&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N118" s="1"/>
       <x:c r="O118" s="1"/>
     </x:row>
@@ -12974,8 +13557,13 @@
         <x:f>IF(ISNUMBER(J119),IF(J119&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L119" s="1"/>
-      <x:c r="M119" s="1"/>
+      <x:c r="L119" s="19" t="n">
+        <x:v>5.8</x:v>
+      </x:c>
+      <x:c r="M119" s="18" t="str">
+        <x:f>IF(ISNUMBER(L119),IF(L119&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N119" s="1"/>
       <x:c r="O119" s="1"/>
     </x:row>
@@ -13014,8 +13602,13 @@
         <x:f>IF(ISNUMBER(J120),IF(J120&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L120" s="1"/>
-      <x:c r="M120" s="1"/>
+      <x:c r="L120" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M120" s="18" t="str">
+        <x:f>IF(ISNUMBER(L120),IF(L120&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N120" s="1"/>
       <x:c r="O120" s="1"/>
     </x:row>
@@ -13054,8 +13647,13 @@
         <x:f>IF(ISNUMBER(J121),IF(J121&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L121" s="1"/>
-      <x:c r="M121" s="1"/>
+      <x:c r="L121" s="19" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="M121" s="18" t="str">
+        <x:f>IF(ISNUMBER(L121),IF(L121&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N121" s="1"/>
       <x:c r="O121" s="1"/>
     </x:row>
@@ -13094,8 +13692,13 @@
         <x:f>IF(ISNUMBER(J122),IF(J122&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L122" s="1"/>
-      <x:c r="M122" s="1"/>
+      <x:c r="L122" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="M122" s="18" t="str">
+        <x:f>IF(ISNUMBER(L122),IF(L122&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N122" s="1"/>
       <x:c r="O122" s="1"/>
     </x:row>
@@ -13134,8 +13737,13 @@
         <x:f>IF(ISNUMBER(J123),IF(J123&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L123" s="1"/>
-      <x:c r="M123" s="1"/>
+      <x:c r="L123" s="19" t="n">
+        <x:v>-2.2</x:v>
+      </x:c>
+      <x:c r="M123" s="18" t="str">
+        <x:f>IF(ISNUMBER(L123),IF(L123&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N123" s="1"/>
       <x:c r="O123" s="1"/>
     </x:row>
@@ -13174,8 +13782,13 @@
         <x:f>IF(ISNUMBER(J124),IF(J124&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L124" s="1"/>
-      <x:c r="M124" s="1"/>
+      <x:c r="L124" s="19" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="M124" s="18" t="str">
+        <x:f>IF(ISNUMBER(L124),IF(L124&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N124" s="1"/>
       <x:c r="O124" s="1"/>
     </x:row>
@@ -13214,8 +13827,13 @@
         <x:f>IF(ISNUMBER(J125),IF(J125&gt;3,"是","否"),"跳过")</x:f>
         <x:v>跳过</x:v>
       </x:c>
-      <x:c r="L125" s="1"/>
-      <x:c r="M125" s="1"/>
+      <x:c r="L125" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M125" s="18" t="str">
+        <x:f>IF(ISNUMBER(L125),IF(L125&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>跳过</x:v>
+      </x:c>
       <x:c r="N125" s="1"/>
       <x:c r="O125" s="1"/>
     </x:row>
@@ -13254,8 +13872,13 @@
         <x:f>IF(ISNUMBER(J126),IF(J126&gt;3,"是","否"),"跳过")</x:f>
         <x:v>跳过</x:v>
       </x:c>
-      <x:c r="L126" s="1"/>
-      <x:c r="M126" s="1"/>
+      <x:c r="L126" s="19" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="M126" s="18" t="str">
+        <x:f>IF(ISNUMBER(L126),IF(L126&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N126" s="1"/>
       <x:c r="O126" s="1"/>
     </x:row>
@@ -13294,8 +13917,13 @@
         <x:f>IF(ISNUMBER(J127),IF(J127&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L127" s="1"/>
-      <x:c r="M127" s="1"/>
+      <x:c r="L127" s="19" t="n">
+        <x:v>-7.1</x:v>
+      </x:c>
+      <x:c r="M127" s="18" t="str">
+        <x:f>IF(ISNUMBER(L127),IF(L127&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N127" s="1"/>
       <x:c r="O127" s="1"/>
     </x:row>
@@ -13334,8 +13962,13 @@
         <x:f>IF(ISNUMBER(J128),IF(J128&gt;3,"是","否"),"跳过")</x:f>
         <x:v>跳过</x:v>
       </x:c>
-      <x:c r="L128" s="1"/>
-      <x:c r="M128" s="1"/>
+      <x:c r="L128" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M128" s="18" t="str">
+        <x:f>IF(ISNUMBER(L128),IF(L128&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>跳过</x:v>
+      </x:c>
       <x:c r="N128" s="1"/>
       <x:c r="O128" s="1"/>
     </x:row>
@@ -13374,8 +14007,13 @@
         <x:f>IF(ISNUMBER(J129),IF(J129&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L129" s="1"/>
-      <x:c r="M129" s="1"/>
+      <x:c r="L129" s="19" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="M129" s="18" t="str">
+        <x:f>IF(ISNUMBER(L129),IF(L129&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N129" s="1"/>
       <x:c r="O129" s="1"/>
     </x:row>
@@ -13414,8 +14052,13 @@
         <x:f>IF(ISNUMBER(J130),IF(J130&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L130" s="1"/>
-      <x:c r="M130" s="1"/>
+      <x:c r="L130" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M130" s="18" t="str">
+        <x:f>IF(ISNUMBER(L130),IF(L130&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N130" s="1"/>
       <x:c r="O130" s="1"/>
     </x:row>
@@ -13454,8 +14097,13 @@
         <x:f>IF(ISNUMBER(J131),IF(J131&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L131" s="1"/>
-      <x:c r="M131" s="1"/>
+      <x:c r="L131" s="19" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="M131" s="18" t="str">
+        <x:f>IF(ISNUMBER(L131),IF(L131&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N131" s="1"/>
       <x:c r="O131" s="1"/>
     </x:row>
@@ -13494,8 +14142,13 @@
         <x:f>IF(ISNUMBER(J132),IF(J132&gt;3,"是","否"),"跳过")</x:f>
         <x:v>跳过</x:v>
       </x:c>
-      <x:c r="L132" s="1"/>
-      <x:c r="M132" s="1"/>
+      <x:c r="L132" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M132" s="18" t="str">
+        <x:f>IF(ISNUMBER(L132),IF(L132&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>跳过</x:v>
+      </x:c>
       <x:c r="N132" s="1"/>
       <x:c r="O132" s="1"/>
     </x:row>
@@ -13534,8 +14187,13 @@
         <x:f>IF(ISNUMBER(J133),IF(J133&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L133" s="1"/>
-      <x:c r="M133" s="1"/>
+      <x:c r="L133" s="19" t="n">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M133" s="18" t="str">
+        <x:f>IF(ISNUMBER(L133),IF(L133&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N133" s="1"/>
       <x:c r="O133" s="1"/>
     </x:row>
@@ -13574,8 +14232,13 @@
         <x:f>IF(ISNUMBER(J134),IF(J134&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L134" s="1"/>
-      <x:c r="M134" s="1"/>
+      <x:c r="L134" s="19" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="M134" s="18" t="str">
+        <x:f>IF(ISNUMBER(L134),IF(L134&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N134" s="1"/>
       <x:c r="O134" s="1"/>
     </x:row>
@@ -13614,8 +14277,13 @@
         <x:f>IF(ISNUMBER(J135),IF(J135&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L135" s="1"/>
-      <x:c r="M135" s="1"/>
+      <x:c r="L135" s="19" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="M135" s="18" t="str">
+        <x:f>IF(ISNUMBER(L135),IF(L135&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N135" s="1"/>
       <x:c r="O135" s="1"/>
     </x:row>
@@ -13654,8 +14322,13 @@
         <x:f>IF(ISNUMBER(J136),IF(J136&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L136" s="1"/>
-      <x:c r="M136" s="1"/>
+      <x:c r="L136" s="19" t="n">
+        <x:v>-4.5</x:v>
+      </x:c>
+      <x:c r="M136" s="18" t="str">
+        <x:f>IF(ISNUMBER(L136),IF(L136&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N136" s="1"/>
       <x:c r="O136" s="1"/>
     </x:row>
@@ -13694,8 +14367,13 @@
         <x:f>IF(ISNUMBER(J137),IF(J137&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L137" s="1"/>
-      <x:c r="M137" s="1"/>
+      <x:c r="L137" s="19" t="n">
+        <x:v>-0.9</x:v>
+      </x:c>
+      <x:c r="M137" s="18" t="str">
+        <x:f>IF(ISNUMBER(L137),IF(L137&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N137" s="1"/>
       <x:c r="O137" s="1"/>
     </x:row>
@@ -13734,8 +14412,13 @@
         <x:f>IF(ISNUMBER(J138),IF(J138&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L138" s="1"/>
-      <x:c r="M138" s="1"/>
+      <x:c r="L138" s="19" t="n">
+        <x:v>-1.9</x:v>
+      </x:c>
+      <x:c r="M138" s="18" t="str">
+        <x:f>IF(ISNUMBER(L138),IF(L138&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N138" s="1"/>
       <x:c r="O138" s="1"/>
     </x:row>
@@ -13774,8 +14457,13 @@
         <x:f>IF(ISNUMBER(J139),IF(J139&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L139" s="1"/>
-      <x:c r="M139" s="1"/>
+      <x:c r="L139" s="19" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="M139" s="18" t="str">
+        <x:f>IF(ISNUMBER(L139),IF(L139&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N139" s="1"/>
       <x:c r="O139" s="1"/>
     </x:row>
@@ -13814,8 +14502,13 @@
         <x:f>IF(ISNUMBER(J140),IF(J140&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L140" s="1"/>
-      <x:c r="M140" s="1"/>
+      <x:c r="L140" s="19" t="n">
+        <x:v>9.6</x:v>
+      </x:c>
+      <x:c r="M140" s="18" t="str">
+        <x:f>IF(ISNUMBER(L140),IF(L140&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N140" s="1"/>
       <x:c r="O140" s="1"/>
     </x:row>
@@ -13854,8 +14547,13 @@
         <x:f>IF(ISNUMBER(J141),IF(J141&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L141" s="1"/>
-      <x:c r="M141" s="1"/>
+      <x:c r="L141" s="19" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="M141" s="18" t="str">
+        <x:f>IF(ISNUMBER(L141),IF(L141&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N141" s="1"/>
       <x:c r="O141" s="1"/>
     </x:row>
@@ -13894,8 +14592,13 @@
         <x:f>IF(ISNUMBER(J142),IF(J142&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L142" s="1"/>
-      <x:c r="M142" s="1"/>
+      <x:c r="L142" s="19" t="n">
+        <x:v>-1.4</x:v>
+      </x:c>
+      <x:c r="M142" s="18" t="str">
+        <x:f>IF(ISNUMBER(L142),IF(L142&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N142" s="1"/>
       <x:c r="O142" s="1"/>
     </x:row>
@@ -13934,8 +14637,13 @@
         <x:f>IF(ISNUMBER(J143),IF(J143&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L143" s="1"/>
-      <x:c r="M143" s="1"/>
+      <x:c r="L143" s="19" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="M143" s="18" t="str">
+        <x:f>IF(ISNUMBER(L143),IF(L143&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N143" s="1"/>
       <x:c r="O143" s="1"/>
     </x:row>
@@ -13974,8 +14682,13 @@
         <x:f>IF(ISNUMBER(J144),IF(J144&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L144" s="1"/>
-      <x:c r="M144" s="1"/>
+      <x:c r="L144" s="19" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="M144" s="18" t="str">
+        <x:f>IF(ISNUMBER(L144),IF(L144&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N144" s="1"/>
       <x:c r="O144" s="1"/>
     </x:row>
@@ -14014,8 +14727,13 @@
         <x:f>IF(ISNUMBER(J145),IF(J145&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L145" s="1"/>
-      <x:c r="M145" s="1"/>
+      <x:c r="L145" s="19" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="M145" s="18" t="str">
+        <x:f>IF(ISNUMBER(L145),IF(L145&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N145" s="1"/>
       <x:c r="O145" s="1"/>
     </x:row>
@@ -14054,8 +14772,13 @@
         <x:f>IF(ISNUMBER(J146),IF(J146&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L146" s="1"/>
-      <x:c r="M146" s="1"/>
+      <x:c r="L146" s="19" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="M146" s="18" t="str">
+        <x:f>IF(ISNUMBER(L146),IF(L146&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N146" s="1"/>
       <x:c r="O146" s="1"/>
     </x:row>
@@ -14094,8 +14817,13 @@
         <x:f>IF(ISNUMBER(J147),IF(J147&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L147" s="1"/>
-      <x:c r="M147" s="1"/>
+      <x:c r="L147" s="19" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="M147" s="18" t="str">
+        <x:f>IF(ISNUMBER(L147),IF(L147&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N147" s="1"/>
       <x:c r="O147" s="1"/>
     </x:row>
@@ -14134,8 +14862,13 @@
         <x:f>IF(ISNUMBER(J148),IF(J148&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L148" s="1"/>
-      <x:c r="M148" s="1"/>
+      <x:c r="L148" s="19" t="n">
+        <x:v>-0.8</x:v>
+      </x:c>
+      <x:c r="M148" s="18" t="str">
+        <x:f>IF(ISNUMBER(L148),IF(L148&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N148" s="1"/>
       <x:c r="O148" s="1"/>
     </x:row>
@@ -14174,8 +14907,13 @@
         <x:f>IF(ISNUMBER(J149),IF(J149&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L149" s="1"/>
-      <x:c r="M149" s="1"/>
+      <x:c r="L149" s="19" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="M149" s="18" t="str">
+        <x:f>IF(ISNUMBER(L149),IF(L149&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N149" s="1"/>
       <x:c r="O149" s="1"/>
     </x:row>
@@ -14214,8 +14952,13 @@
         <x:f>IF(ISNUMBER(J150),IF(J150&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L150" s="1"/>
-      <x:c r="M150" s="1"/>
+      <x:c r="L150" s="19" t="n">
+        <x:v>6.6</x:v>
+      </x:c>
+      <x:c r="M150" s="18" t="str">
+        <x:f>IF(ISNUMBER(L150),IF(L150&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N150" s="1"/>
       <x:c r="O150" s="1"/>
     </x:row>
@@ -14254,8 +14997,13 @@
         <x:f>IF(ISNUMBER(J151),IF(J151&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L151" s="1"/>
-      <x:c r="M151" s="1"/>
+      <x:c r="L151" s="19" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="M151" s="18" t="str">
+        <x:f>IF(ISNUMBER(L151),IF(L151&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N151" s="1"/>
       <x:c r="O151" s="1"/>
     </x:row>
@@ -14294,8 +15042,13 @@
         <x:f>IF(ISNUMBER(J152),IF(J152&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L152" s="1"/>
-      <x:c r="M152" s="1"/>
+      <x:c r="L152" s="19" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="M152" s="18" t="str">
+        <x:f>IF(ISNUMBER(L152),IF(L152&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N152" s="1"/>
       <x:c r="O152" s="1"/>
     </x:row>
@@ -14334,8 +15087,13 @@
         <x:f>IF(ISNUMBER(J153),IF(J153&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L153" s="1"/>
-      <x:c r="M153" s="1"/>
+      <x:c r="L153" s="19" t="n">
+        <x:v>-1.1</x:v>
+      </x:c>
+      <x:c r="M153" s="18" t="str">
+        <x:f>IF(ISNUMBER(L153),IF(L153&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N153" s="1"/>
       <x:c r="O153" s="1"/>
     </x:row>
@@ -14374,8 +15132,13 @@
         <x:f>IF(ISNUMBER(J154),IF(J154&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L154" s="1"/>
-      <x:c r="M154" s="1"/>
+      <x:c r="L154" s="19" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="M154" s="18" t="str">
+        <x:f>IF(ISNUMBER(L154),IF(L154&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N154" s="1"/>
       <x:c r="O154" s="1"/>
     </x:row>
@@ -14414,8 +15177,13 @@
         <x:f>IF(ISNUMBER(J155),IF(J155&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L155" s="1"/>
-      <x:c r="M155" s="1"/>
+      <x:c r="L155" s="19" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="M155" s="18" t="str">
+        <x:f>IF(ISNUMBER(L155),IF(L155&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N155" s="1"/>
       <x:c r="O155" s="1"/>
     </x:row>
@@ -14454,8 +15222,13 @@
         <x:f>IF(ISNUMBER(J156),IF(J156&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L156" s="1"/>
-      <x:c r="M156" s="1"/>
+      <x:c r="L156" s="19" t="n">
+        <x:v>15.2</x:v>
+      </x:c>
+      <x:c r="M156" s="18" t="str">
+        <x:f>IF(ISNUMBER(L156),IF(L156&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N156" s="1"/>
       <x:c r="O156" s="1"/>
     </x:row>
@@ -14494,8 +15267,13 @@
         <x:f>IF(ISNUMBER(J157),IF(J157&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L157" s="1"/>
-      <x:c r="M157" s="1"/>
+      <x:c r="L157" s="19" t="n">
+        <x:v>-0.7</x:v>
+      </x:c>
+      <x:c r="M157" s="18" t="str">
+        <x:f>IF(ISNUMBER(L157),IF(L157&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N157" s="1"/>
       <x:c r="O157" s="1"/>
     </x:row>
@@ -14534,8 +15312,13 @@
         <x:f>IF(ISNUMBER(J158),IF(J158&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L158" s="1"/>
-      <x:c r="M158" s="1"/>
+      <x:c r="L158" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="M158" s="18" t="str">
+        <x:f>IF(ISNUMBER(L158),IF(L158&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N158" s="1"/>
       <x:c r="O158" s="1"/>
     </x:row>
@@ -14574,8 +15357,13 @@
         <x:f>IF(ISNUMBER(J159),IF(J159&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L159" s="1"/>
-      <x:c r="M159" s="1"/>
+      <x:c r="L159" s="19" t="n">
+        <x:v>-1.5</x:v>
+      </x:c>
+      <x:c r="M159" s="18" t="str">
+        <x:f>IF(ISNUMBER(L159),IF(L159&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N159" s="1"/>
       <x:c r="O159" s="1"/>
     </x:row>
@@ -14614,8 +15402,13 @@
         <x:f>IF(ISNUMBER(J160),IF(J160&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L160" s="1"/>
-      <x:c r="M160" s="1"/>
+      <x:c r="L160" s="19" t="n">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="M160" s="18" t="str">
+        <x:f>IF(ISNUMBER(L160),IF(L160&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N160" s="1"/>
       <x:c r="O160" s="1"/>
     </x:row>
@@ -14654,8 +15447,13 @@
         <x:f>IF(ISNUMBER(J161),IF(J161&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L161" s="1"/>
-      <x:c r="M161" s="1"/>
+      <x:c r="L161" s="19" t="n">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="M161" s="18" t="str">
+        <x:f>IF(ISNUMBER(L161),IF(L161&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N161" s="1"/>
       <x:c r="O161" s="1"/>
     </x:row>
@@ -14694,8 +15492,13 @@
         <x:f>IF(ISNUMBER(J162),IF(J162&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L162" s="1"/>
-      <x:c r="M162" s="1"/>
+      <x:c r="L162" s="19" t="n">
+        <x:v>34.2</x:v>
+      </x:c>
+      <x:c r="M162" s="18" t="str">
+        <x:f>IF(ISNUMBER(L162),IF(L162&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N162" s="1"/>
       <x:c r="O162" s="1"/>
     </x:row>
@@ -14734,8 +15537,13 @@
         <x:f>IF(ISNUMBER(J163),IF(J163&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L163" s="1"/>
-      <x:c r="M163" s="1"/>
+      <x:c r="L163" s="19" t="n">
+        <x:v>60.9</x:v>
+      </x:c>
+      <x:c r="M163" s="18" t="str">
+        <x:f>IF(ISNUMBER(L163),IF(L163&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N163" s="1"/>
       <x:c r="O163" s="1"/>
     </x:row>
@@ -14774,8 +15582,13 @@
         <x:f>IF(ISNUMBER(J164),IF(J164&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L164" s="1"/>
-      <x:c r="M164" s="1"/>
+      <x:c r="L164" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="M164" s="18" t="str">
+        <x:f>IF(ISNUMBER(L164),IF(L164&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N164" s="1"/>
       <x:c r="O164" s="1"/>
     </x:row>
@@ -14814,8 +15627,13 @@
         <x:f>IF(ISNUMBER(J165),IF(J165&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L165" s="1"/>
-      <x:c r="M165" s="1"/>
+      <x:c r="L165" s="19" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="M165" s="18" t="str">
+        <x:f>IF(ISNUMBER(L165),IF(L165&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N165" s="1"/>
       <x:c r="O165" s="1"/>
     </x:row>
@@ -14854,8 +15672,13 @@
         <x:f>IF(ISNUMBER(J166),IF(J166&gt;3,"是","否"),"跳过")</x:f>
         <x:v>跳过</x:v>
       </x:c>
-      <x:c r="L166" s="1"/>
-      <x:c r="M166" s="1"/>
+      <x:c r="L166" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M166" s="18" t="str">
+        <x:f>IF(ISNUMBER(L166),IF(L166&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N166" s="1"/>
       <x:c r="O166" s="1"/>
     </x:row>
@@ -14894,8 +15717,13 @@
         <x:f>IF(ISNUMBER(J167),IF(J167&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L167" s="1"/>
-      <x:c r="M167" s="1"/>
+      <x:c r="L167" s="19" t="n">
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="M167" s="18" t="str">
+        <x:f>IF(ISNUMBER(L167),IF(L167&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N167" s="1"/>
       <x:c r="O167" s="1"/>
     </x:row>
@@ -14934,8 +15762,13 @@
         <x:f>IF(ISNUMBER(J168),IF(J168&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L168" s="1"/>
-      <x:c r="M168" s="1"/>
+      <x:c r="L168" s="19" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="M168" s="18" t="str">
+        <x:f>IF(ISNUMBER(L168),IF(L168&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N168" s="1"/>
       <x:c r="O168" s="1"/>
     </x:row>
@@ -14974,8 +15807,13 @@
         <x:f>IF(ISNUMBER(J169),IF(J169&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L169" s="1"/>
-      <x:c r="M169" s="1"/>
+      <x:c r="L169" s="19" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="M169" s="18" t="str">
+        <x:f>IF(ISNUMBER(L169),IF(L169&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N169" s="1"/>
       <x:c r="O169" s="1"/>
     </x:row>
@@ -15014,8 +15852,13 @@
         <x:f>IF(ISNUMBER(J170),IF(J170&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L170" s="1"/>
-      <x:c r="M170" s="1"/>
+      <x:c r="L170" s="19" t="n">
+        <x:v>-3.4</x:v>
+      </x:c>
+      <x:c r="M170" s="18" t="str">
+        <x:f>IF(ISNUMBER(L170),IF(L170&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N170" s="1"/>
       <x:c r="O170" s="1"/>
     </x:row>
@@ -15054,8 +15897,13 @@
         <x:f>IF(ISNUMBER(J171),IF(J171&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L171" s="1"/>
-      <x:c r="M171" s="1"/>
+      <x:c r="L171" s="19" t="n">
+        <x:v>22.4</x:v>
+      </x:c>
+      <x:c r="M171" s="18" t="str">
+        <x:f>IF(ISNUMBER(L171),IF(L171&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N171" s="1"/>
       <x:c r="O171" s="1"/>
     </x:row>
@@ -15094,8 +15942,13 @@
         <x:f>IF(ISNUMBER(J172),IF(J172&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L172" s="1"/>
-      <x:c r="M172" s="1"/>
+      <x:c r="L172" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="M172" s="18" t="str">
+        <x:f>IF(ISNUMBER(L172),IF(L172&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N172" s="1"/>
       <x:c r="O172" s="1"/>
     </x:row>
@@ -15134,8 +15987,13 @@
         <x:f>IF(ISNUMBER(J173),IF(J173&gt;3,"是","否"),"跳过")</x:f>
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L173" s="1"/>
-      <x:c r="M173" s="1"/>
+      <x:c r="L173" s="19" t="n">
+        <x:v>9.6</x:v>
+      </x:c>
+      <x:c r="M173" s="18" t="str">
+        <x:f>IF(ISNUMBER(L173),IF(L173&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N173" s="1"/>
       <x:c r="O173" s="1"/>
     </x:row>
@@ -15174,8 +16032,13 @@
         <x:f>IF(ISNUMBER(J174),IF(J174&gt;3,"是","否"),"跳过")</x:f>
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L174" s="1"/>
-      <x:c r="M174" s="1"/>
+      <x:c r="L174" s="19" t="n">
+        <x:v>-9</x:v>
+      </x:c>
+      <x:c r="M174" s="18" t="str">
+        <x:f>IF(ISNUMBER(L174),IF(L174&gt;3,"是","否"),"跳过")</x:f>
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N174" s="1"/>
       <x:c r="O174" s="1"/>
     </x:row>
@@ -15210,8 +16073,8 @@
       <x:c r="I176" s="14"/>
       <x:c r="J176" s="14"/>
       <x:c r="K176" s="14"/>
-      <x:c r="L176" s="1"/>
-      <x:c r="M176" s="1"/>
+      <x:c r="L176" s="14"/>
+      <x:c r="M176" s="14"/>
       <x:c r="N176" s="1"/>
       <x:c r="O176" s="1"/>
     </x:row>
@@ -15250,7 +16113,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="K177" s="1"/>
-      <x:c r="L177" s="1"/>
+      <x:c r="L177" s="1" t="n">
+        <x:f>COUNT(L5:L174)</x:f>
+        <x:v>166</x:v>
+      </x:c>
       <x:c r="M177" s="1"/>
       <x:c r="N177" s="1"/>
       <x:c r="O177" s="1"/>
@@ -15290,7 +16156,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="K178" s="1"/>
-      <x:c r="L178" s="1"/>
+      <x:c r="L178" s="1" t="n">
+        <x:f>COUNTIF(L5:L174,"&gt;3")</x:f>
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="M178" s="1"/>
       <x:c r="N178" s="1"/>
       <x:c r="O178" s="1"/>
@@ -15330,7 +16199,10 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="K179" s="1"/>
-      <x:c r="L179" s="1"/>
+      <x:c r="L179" s="16" t="n">
+        <x:f>IF(L177=0,0,L178/L177)</x:f>
+        <x:v>0.4759036144578313</x:v>
+      </x:c>
       <x:c r="M179" s="1"/>
       <x:c r="N179" s="1"/>
       <x:c r="O179" s="1"/>
@@ -16123,7 +16995,7 @@
         <x:v>https://www.atlantafed.org/research-and-data/data/wage-growth-tracker</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>月更；通常在每月第二个周五前后更新。最新值 2026-09=3.9%，对齐值 2026-08=4.1%。</x:v>
+        <x:v>月更；最新值 2026-09=3.9%，前月 2026-08=4.1%。</x:v>
       </x:c>
       <x:c r="E4" s="1"/>
       <x:c r="F4" s="1"/>
@@ -16148,7 +17020,7 @@
         <x:v>https://fred.stlouisfed.org/data/STICKCPIM159SFRBATL</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>月更；CPI发布日期当日发布。历史和当前数值取Atlanta Fed序列，经FRED展示。</x:v>
+        <x:v>月更；本期 2026-09=2.815533730%，更新日 2026-10-14。</x:v>
       </x:c>
       <x:c r="E5" s="1"/>
       <x:c r="F5" s="1"/>
@@ -16173,7 +17045,7 @@
         <x:v>https://fred.stlouisfed.org/data/FLEXCPIM159SFRBATL</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>月更；CPI发布日期当日发布。历史和当前数值取Atlanta Fed序列，经FRED展示。</x:v>
+        <x:v>月更；本期 2026-09=6.123248688%，更新日 2026-10-14。</x:v>
       </x:c>
       <x:c r="E6" s="1"/>
       <x:c r="F6" s="1"/>
@@ -16198,7 +17070,7 @@
         <x:v>https://www.bls.gov/news.release/cpi.t02.htm</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>月更；使用BLS页面显示值（1位小数）。本期 2026-08 为 82/164。</x:v>
+        <x:v>月更；BLS页面显示一位小数；本期 2026-09 为 79/166=47.6%。</x:v>
       </x:c>
       <x:c r="E7" s="1"/>
       <x:c r="F7" s="1"/>
@@ -16223,7 +17095,7 @@
         <x:v>https://www.bls.gov/cpi/additional-resources/cpi-item-aggregation.htm</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>其余41项不填补、不代理；覆盖率独立显示。BLS表内汇总行与SS特殊相对指数不作为互斥细项重复计数。</x:v>
+        <x:v>其余41项不填补、不代理；本期数值覆盖为166/211=78.7%。表中汇总行和SS特殊相对指数不作为互斥细项重复计数。</x:v>
       </x:c>
       <x:c r="E8" s="1"/>
       <x:c r="F8" s="1"/>
@@ -16273,7 +17145,7 @@
         <x:v>https://www.bls.gov/news.release/cpi.t02.htm</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
-        <x:v>逐月分母为有数值的行数；因子4明细表保留“—”与“空白”状态。</x:v>
+        <x:v>BLS同比列显示破折号或空白时，既不计入&gt;3%项目，也不计入分母。2026-09本次4项破折号，已映射行无数值空白。</x:v>
       </x:c>
       <x:c r="E10" s="1"/>
       <x:c r="F10" s="1"/>
@@ -16392,13 +17264,13 @@
         <x:v>阶段判断边界</x:v>
       </x:c>
       <x:c r="B15" s="18" t="str">
-        <x:v>当前 53.77（最新可得混合期）/54.60（2026-08同月对齐）均低于100基准。</x:v>
+        <x:v>当前 55.02（2026-09）；前月 54.60（2026-08），均低于100基准。</x:v>
       </x:c>
       <x:c r="C15" s="18" t="str">
         <x:v>https://www.atlantafed.org/research-and-data/data/wage-growth-tracker</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>这说明低于2022H1通胀压力基准，不足以单独定义投资风险阶段；需先回测阈值。</x:v>
+        <x:v>这只表示低于2022H1通胀压力基准，不能单独定义投资风险阶段；阶段阈值需历史回测后确定。</x:v>
       </x:c>
       <x:c r="E15" s="1"/>
       <x:c r="F15" s="1"/>
